--- a/src/service_ia/dataset/analyze_statistics.xlsx
+++ b/src/service_ia/dataset/analyze_statistics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,528 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id_fixture</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date_fixture</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>round_fixture</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>team_id</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>opponent_id</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>opponent_name</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>type_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>946798</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2022-10-06T19:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Group Stage - 3</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>209</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Feyenoord</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>397</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>946806</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2022-10-13T16:45:00+00:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Group Stage - 4</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>209</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Feyenoord</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>397</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>946828</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2022-10-27T19:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Group Stage - 5</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>209</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Feyenoord</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>637</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sturm Graz</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1010836</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2023-03-09T20:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Round of 16</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>209</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Feyenoord</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>550</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Shakhtar Donetsk</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1010837</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2023-03-16T17:45:00+00:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Round of 16</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>209</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Feyenoord</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>550</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Shakhtar Donetsk</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1287616</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024-08-22T18:45:00+00:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Play-offs</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>194</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>336</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Jagiellonia</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1299128</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024-09-25T16:45:00+00:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>League Stage - 1</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>201</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>372</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>IF Elfsborg</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1299153</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-10-03T16:45:00+00:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>League Stage - 2</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>194</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>560</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Slavia Praha</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1299171</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024-10-24T16:45:00+00:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>League Stage - 3</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>194</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>556</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Qarabag</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1299192</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024-11-07T20:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>League Stage - 4</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>194</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>604</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1299209</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2024-11-28T20:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>League Stage - 5</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>415</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1393</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Union St. Gilloise</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1299219</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2024-12-12T17:45:00+00:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>League Stage - 6</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>201</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>566</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ludogorets</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1299221</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2024-12-12T17:45:00+00:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>League Stage - 6</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>415</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>553</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Olympiakos Piraeus</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1345757</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-02-13T17:45:00+00:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Knockout Round Play-offs</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>194</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1393</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Union St. Gilloise</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>